--- a/outputs/Block5B_Senate_Historic_Clean.xlsx
+++ b/outputs/Block5B_Senate_Historic_Clean.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="53">
   <si>
     <t>STATE</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>Flip</t>
+  </si>
+  <si>
+    <t>MEDSL Result Margin 2P v28</t>
+  </si>
+  <si>
+    <t>MEDSL Result Difference PP v28</t>
   </si>
   <si>
     <t>National Vote Margin 2P</t>
@@ -524,10 +530,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL35"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:38">
+    <row r="1" spans="1:40">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -642,19 +648,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:38">
+    <row r="2" spans="1:40">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>2010</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -696,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -708,69 +720,75 @@
         <v>0</v>
       </c>
       <c r="V2">
+        <v>-12.05230466961249</v>
+      </c>
+      <c r="W2">
+        <v>-13.41234981807614</v>
+      </c>
+      <c r="X2">
         <v>-10.21739130434782</v>
       </c>
-      <c r="W2">
-        <v>6.472354736093108</v>
-      </c>
-      <c r="X2">
-        <v>0.2591279874364147</v>
-      </c>
       <c r="Y2">
-        <v>-6.213226748656693</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>6.731482723529522</v>
+        <v>0</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.2591279874364147</v>
+        <v>0</v>
       </c>
       <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
         <v>0.6145730225123781</v>
       </c>
-      <c r="AD2">
+      <c r="AF2">
         <v>0.5927039999999999</v>
       </c>
-      <c r="AE2">
+      <c r="AG2">
         <v>0.3642598887351765</v>
       </c>
-      <c r="AF2">
-        <v>-4.340182019074399</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
       <c r="AH2">
+        <v>-1.749476804006003</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
         <v>-25.46465448768863</v>
       </c>
-      <c r="AI2">
+      <c r="AK2">
         <v>0.5</v>
       </c>
-      <c r="AJ2">
+      <c r="AL2">
         <v>9.27312129748907</v>
       </c>
-      <c r="AK2">
+      <c r="AM2">
         <v>-6.252657710366077</v>
       </c>
-      <c r="AL2">
+      <c r="AN2">
         <v>-19.21199677732256</v>
       </c>
     </row>
-    <row r="3" spans="1:38">
+    <row r="3" spans="1:40">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>2014</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3">
         <v>43.8</v>
@@ -812,10 +830,10 @@
         <v>2.666666666666671</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -824,69 +842,75 @@
         <v>1</v>
       </c>
       <c r="V3">
+        <v>-2.129603399433427</v>
+      </c>
+      <c r="W3">
+        <v>-0.1414276273284836</v>
+      </c>
+      <c r="X3">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W3">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X3">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y3">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <v>1</v>
       </c>
-      <c r="AB3">
-        <v>-4.810009664065643</v>
-      </c>
-      <c r="AC3">
+      <c r="AD3">
+        <v>-0</v>
+      </c>
+      <c r="AE3">
         <v>0.91875459182526</v>
       </c>
-      <c r="AD3">
+      <c r="AF3">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE3">
+      <c r="AG3">
         <v>0.6482732399919033</v>
       </c>
-      <c r="AF3">
-        <v>-2.740166932561301</v>
-      </c>
-      <c r="AG3">
-        <v>-2.666666666666671</v>
-      </c>
       <c r="AH3">
-        <v>0.3956356399047607</v>
+        <v>-2.658273994120623</v>
       </c>
       <c r="AI3">
-        <v>0.3868381550465201</v>
+        <v>-2.662470330393647</v>
       </c>
       <c r="AJ3">
-        <v>9.27312129748907</v>
+        <v>0.3914393036317363</v>
       </c>
       <c r="AK3">
-        <v>-2.567427654608816</v>
+        <v>0.2987785157810103</v>
       </c>
       <c r="AL3">
-        <v>2.963063294513577</v>
+        <v>5.043351435174619</v>
+      </c>
+      <c r="AM3">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN3">
+        <v>3.378982242168426</v>
       </c>
     </row>
-    <row r="4" spans="1:38">
+    <row r="4" spans="1:40">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>2022</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E4">
         <v>14</v>
@@ -928,10 +952,10 @@
         <v>46.15384615384615</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -940,69 +964,75 @@
         <v>0</v>
       </c>
       <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>-61.40677335318199</v>
+      </c>
+      <c r="X4">
         <v>-2.67379679144385</v>
       </c>
-      <c r="W4">
-        <v>3.770648896483239</v>
-      </c>
-      <c r="X4">
-        <v>2.083268974682547</v>
-      </c>
       <c r="Y4">
-        <v>-1.687379921800692</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>5.853917871165787</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.083268974682547</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>0.5286284139166187</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0.5286284139166187</v>
       </c>
       <c r="AF4">
-        <v>-57.34220048224016</v>
+        <v>1</v>
       </c>
       <c r="AG4">
-        <v>-54.54511190014166</v>
+        <v>0.5286284139166187</v>
       </c>
       <c r="AH4">
-        <v>-6.861661453040334</v>
+        <v>-58.82832630389451</v>
       </c>
       <c r="AI4">
+        <v>-58.82832630389451</v>
+      </c>
+      <c r="AJ4">
+        <v>-2.578447049287483</v>
+      </c>
+      <c r="AK4">
         <v>0.001</v>
       </c>
-      <c r="AJ4">
-        <v>8.360348690750994</v>
-      </c>
-      <c r="AK4">
-        <v>2.12594030235794</v>
-      </c>
       <c r="AL4">
-        <v>-8.987601755398273</v>
+        <v>8.315992646425135</v>
+      </c>
+      <c r="AM4">
+        <v>4.262691039343795</v>
+      </c>
+      <c r="AN4">
+        <v>-6.841138088631278</v>
       </c>
     </row>
-    <row r="5" spans="1:38">
+    <row r="5" spans="1:40">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>2010</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E5">
         <v>32.8</v>
@@ -1044,10 +1074,10 @@
         <v>27.19200887902331</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -1056,69 +1086,75 @@
         <v>0</v>
       </c>
       <c r="V5">
+        <v>-19.30873516490312</v>
+      </c>
+      <c r="W5">
+        <v>-0.5350630058912387</v>
+      </c>
+      <c r="X5">
         <v>-10.21739130434782</v>
       </c>
-      <c r="W5">
-        <v>6.472354736093108</v>
-      </c>
-      <c r="X5">
-        <v>0.2591279874364147</v>
-      </c>
       <c r="Y5">
-        <v>-6.213226748656693</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>6.731482723529522</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.2591279874364147</v>
+        <v>0</v>
       </c>
       <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
         <v>0.9363562890267786</v>
       </c>
-      <c r="AD5">
+      <c r="AF5">
         <v>0.5927039999999999</v>
       </c>
-      <c r="AE5">
+      <c r="AG5">
         <v>0.5549821179313277</v>
       </c>
-      <c r="AF5">
-        <v>-30.09168861960553</v>
-      </c>
-      <c r="AG5">
+      <c r="AH5">
+        <v>-27.46616089753333</v>
+      </c>
+      <c r="AI5">
         <v>-27.19200887902331</v>
       </c>
-      <c r="AH5">
+      <c r="AJ5">
         <v>7.348210708228947</v>
       </c>
-      <c r="AI5">
+      <c r="AK5">
         <v>0.001</v>
       </c>
-      <c r="AJ5">
+      <c r="AL5">
         <v>6.306372390821725</v>
       </c>
-      <c r="AK5">
+      <c r="AM5">
         <v>-6.252657710366077</v>
       </c>
-      <c r="AL5">
+      <c r="AN5">
         <v>13.60086841859502</v>
       </c>
     </row>
-    <row r="6" spans="1:38">
+    <row r="6" spans="1:40">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>2014</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>45.4</v>
@@ -1160,10 +1196,10 @@
         <v>2.991452991452995</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -1172,69 +1208,75 @@
         <v>0</v>
       </c>
       <c r="V6">
+        <v>-7.682709551543054</v>
+      </c>
+      <c r="W6">
+        <v>-0.1460366258269747</v>
+      </c>
+      <c r="X6">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W6">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X6">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y6">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.8299339386406256</v>
+        <v>0</v>
       </c>
       <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
         <v>0.9582358791028438</v>
       </c>
-      <c r="AD6">
+      <c r="AF6">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE6">
+      <c r="AG6">
         <v>0.6761312362949665</v>
       </c>
-      <c r="AF6">
-        <v>-3.18930072759332</v>
-      </c>
-      <c r="AG6">
-        <v>-2.991452991452995</v>
-      </c>
       <c r="AH6">
-        <v>-4.837293185917034</v>
+        <v>-5.551894403746672</v>
       </c>
       <c r="AI6">
-        <v>0.3817745054893844</v>
+        <v>-4.271673697599834</v>
       </c>
       <c r="AJ6">
-        <v>9.944209787481359</v>
+        <v>-3.557072479770195</v>
       </c>
       <c r="AK6">
-        <v>-2.567427654608816</v>
+        <v>0.2178221736430758</v>
       </c>
       <c r="AL6">
-        <v>-2.269865531308218</v>
+        <v>5.479529412288271</v>
+      </c>
+      <c r="AM6">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN6">
+        <v>-0.5695295412335049</v>
       </c>
     </row>
-    <row r="7" spans="1:38">
+    <row r="7" spans="1:40">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>2022</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E7">
         <v>47.4</v>
@@ -1276,10 +1318,10 @@
         <v>1.455301455301452</v>
       </c>
       <c r="R7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T7" t="b">
         <v>1</v>
@@ -1288,69 +1330,75 @@
         <v>0</v>
       </c>
       <c r="V7">
+        <v>0.9572085233353123</v>
+      </c>
+      <c r="W7">
+        <v>1.842791476664685</v>
+      </c>
+      <c r="X7">
         <v>-2.67379679144385</v>
       </c>
-      <c r="W7">
-        <v>3.770648896483239</v>
-      </c>
-      <c r="X7">
-        <v>2.083268974682547</v>
-      </c>
       <c r="Y7">
-        <v>-1.687379921800692</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>5.853917871165787</v>
+        <v>0</v>
       </c>
       <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
         <v>1</v>
       </c>
-      <c r="AB7">
-        <v>-3.770648896483239</v>
-      </c>
-      <c r="AC7">
-        <v>0.9808159868191382</v>
-      </c>
       <c r="AD7">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="AE7">
         <v>0.9808159868191382</v>
       </c>
       <c r="AF7">
-        <v>0.003253271547104974</v>
+        <v>1</v>
       </c>
       <c r="AG7">
-        <v>-0.3613854101650343</v>
+        <v>0.9808159868191382</v>
       </c>
       <c r="AH7">
-        <v>3.161385410165031</v>
+        <v>-1.970258657847667</v>
       </c>
       <c r="AI7">
-        <v>0.4760880166957929</v>
+        <v>-1.970258657847667</v>
       </c>
       <c r="AJ7">
-        <v>6.02566232575385</v>
+        <v>4.770258657847664</v>
       </c>
       <c r="AK7">
-        <v>2.12594030235794</v>
+        <v>0.3882341621301975</v>
       </c>
       <c r="AL7">
-        <v>1.035445107807091</v>
+        <v>6.939377955031237</v>
+      </c>
+      <c r="AM7">
+        <v>4.262691039343795</v>
+      </c>
+      <c r="AN7">
+        <v>0.5075676185038693</v>
       </c>
     </row>
-    <row r="8" spans="1:38">
+    <row r="8" spans="1:40">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>2010</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E8">
         <v>39</v>
@@ -1392,10 +1440,10 @@
         <v>13.33333333333333</v>
       </c>
       <c r="R8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -1404,69 +1452,75 @@
         <v>0</v>
       </c>
       <c r="V8">
+        <v>-31.04923288380675</v>
+      </c>
+      <c r="W8">
+        <v>-0.7480021392347105</v>
+      </c>
+      <c r="X8">
         <v>-10.21739130434782</v>
       </c>
-      <c r="W8">
-        <v>6.472354736093108</v>
-      </c>
-      <c r="X8">
-        <v>0.2591279874364147</v>
-      </c>
       <c r="Y8">
-        <v>-6.213226748656693</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>6.731482723529522</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.2591279874364147</v>
+        <v>0</v>
       </c>
       <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
         <v>0.9374699995199847</v>
       </c>
-      <c r="AD8">
+      <c r="AF8">
         <v>0.5927039999999999</v>
       </c>
-      <c r="AE8">
+      <c r="AG8">
         <v>0.5556422185954929</v>
       </c>
-      <c r="AF8">
-        <v>-16.21075837199487</v>
-      </c>
-      <c r="AG8">
+      <c r="AH8">
+        <v>-13.58846687292746</v>
+      </c>
+      <c r="AI8">
         <v>-13.33333333333333</v>
       </c>
-      <c r="AH8">
+      <c r="AJ8">
         <v>-18.46390168970813</v>
       </c>
-      <c r="AI8">
+      <c r="AK8">
         <v>0.0136385293895773</v>
       </c>
-      <c r="AJ8">
+      <c r="AL8">
         <v>6.039933224873137</v>
       </c>
-      <c r="AK8">
+      <c r="AM8">
         <v>-6.252657710366077</v>
       </c>
-      <c r="AL8">
+      <c r="AN8">
         <v>-12.21124397934205</v>
       </c>
     </row>
-    <row r="9" spans="1:38">
+    <row r="9" spans="1:40">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>2014</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9">
         <v>45.7</v>
@@ -1508,10 +1562,10 @@
         <v>2.454642475987193</v>
       </c>
       <c r="R9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -1520,69 +1574,75 @@
         <v>1</v>
       </c>
       <c r="V9">
+        <v>-8.338939541471181</v>
+      </c>
+      <c r="W9">
+        <v>-0.3612482323656643</v>
+      </c>
+      <c r="X9">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W9">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X9">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y9">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
         <v>1</v>
       </c>
-      <c r="AB9">
-        <v>-4.810009664065643</v>
-      </c>
-      <c r="AC9">
+      <c r="AD9">
+        <v>-0</v>
+      </c>
+      <c r="AE9">
         <v>0.9477384660337471</v>
       </c>
-      <c r="AD9">
+      <c r="AF9">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE9">
+      <c r="AG9">
         <v>0.6687242616334119</v>
       </c>
-      <c r="AF9">
-        <v>-2.338121137486801</v>
-      </c>
-      <c r="AG9">
-        <v>-2.454642475987193</v>
-      </c>
       <c r="AH9">
-        <v>-6.245545297849652</v>
+        <v>-0.3168159622798443</v>
       </c>
       <c r="AI9">
-        <v>0.4063280475515493</v>
+        <v>-1.385729219133518</v>
       </c>
       <c r="AJ9">
-        <v>10.35710209019926</v>
+        <v>-7.314458554703327</v>
       </c>
       <c r="AK9">
-        <v>-2.567427654608816</v>
+        <v>0.4078364041737271</v>
       </c>
       <c r="AL9">
-        <v>-3.678117643240836</v>
+        <v>5.944424790175924</v>
+      </c>
+      <c r="AM9">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN9">
+        <v>-4.326915616166637</v>
       </c>
     </row>
-    <row r="10" spans="1:38">
+    <row r="10" spans="1:40">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>2022</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E10">
         <v>41</v>
@@ -1624,10 +1684,10 @@
         <v>12.76595744680851</v>
       </c>
       <c r="R10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -1636,69 +1696,75 @@
         <v>0</v>
       </c>
       <c r="V10">
+        <v>-12.04234990442257</v>
+      </c>
+      <c r="W10">
+        <v>-0.1459325192128862</v>
+      </c>
+      <c r="X10">
         <v>-2.67379679144385</v>
       </c>
-      <c r="W10">
-        <v>3.770648896483239</v>
-      </c>
-      <c r="X10">
-        <v>2.083268974682547</v>
-      </c>
       <c r="Y10">
-        <v>-1.687379921800692</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5.853917871165787</v>
+        <v>0</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.083268974682547</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>0.968808546617958</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0.968808546617958</v>
       </c>
       <c r="AF10">
-        <v>-13.95629209855609</v>
+        <v>1</v>
       </c>
       <c r="AG10">
-        <v>-13.6587084356192</v>
+        <v>0.968808546617958</v>
       </c>
       <c r="AH10">
-        <v>1.47042601198374</v>
+        <v>-15.33749488275634</v>
       </c>
       <c r="AI10">
-        <v>0.007551698746464627</v>
+        <v>-15.33749488275634</v>
       </c>
       <c r="AJ10">
-        <v>5.621121655288039</v>
+        <v>3.149212459120879</v>
       </c>
       <c r="AK10">
-        <v>2.12594030235794</v>
+        <v>0.01206422363196213</v>
       </c>
       <c r="AL10">
-        <v>-0.6555142903741999</v>
+        <v>6.801315253106774</v>
+      </c>
+      <c r="AM10">
+        <v>4.262691039343795</v>
+      </c>
+      <c r="AN10">
+        <v>-1.113478580222917</v>
       </c>
     </row>
-    <row r="11" spans="1:38">
+    <row r="11" spans="1:40">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>2006</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11">
         <v>14</v>
@@ -1740,10 +1806,10 @@
         <v>68.18181818181819</v>
       </c>
       <c r="R11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
@@ -1752,69 +1818,75 @@
         <v>0</v>
       </c>
       <c r="V11">
+        <v>-53.65070222039594</v>
+      </c>
+      <c r="W11">
+        <v>-2.818642388483539</v>
+      </c>
+      <c r="X11">
         <v>12.40560949298812</v>
       </c>
-      <c r="W11">
-        <v>3.14083609983384</v>
-      </c>
-      <c r="X11">
-        <v>1.706744969770823</v>
-      </c>
       <c r="Y11">
-        <v>-1.434091130063018</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>4.847581069604663</v>
+        <v>0</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.706744969770823</v>
+        <v>0</v>
       </c>
       <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
         <v>0.9124034195464197</v>
       </c>
-      <c r="AD11">
+      <c r="AF11">
         <v>0.4978713599999999</v>
       </c>
-      <c r="AE11">
+      <c r="AG11">
         <v>0.4542595313582265</v>
       </c>
-      <c r="AF11">
-        <v>-62.83119647919543</v>
-      </c>
-      <c r="AG11">
-        <v>-62.83119647919543</v>
-      </c>
       <c r="AH11">
-        <v>6.361851870315945</v>
+        <v>-65.17435072854664</v>
       </c>
       <c r="AI11">
+        <v>-67.27957794583672</v>
+      </c>
+      <c r="AJ11">
+        <v>10.81023333695724</v>
+      </c>
+      <c r="AK11">
         <v>0.001</v>
       </c>
-      <c r="AJ11">
-        <v>7.263203911640863</v>
-      </c>
-      <c r="AK11">
-        <v>2.846074341100446</v>
-      </c>
       <c r="AL11">
-        <v>3.515777529215499</v>
+        <v>5.621628320182992</v>
+      </c>
+      <c r="AM11">
+        <v>4.161274749007029</v>
+      </c>
+      <c r="AN11">
+        <v>6.64895858795021</v>
       </c>
     </row>
-    <row r="12" spans="1:38">
+    <row r="12" spans="1:40">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>2014</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12">
         <v>32.2</v>
@@ -1856,10 +1928,10 @@
         <v>31.19658119658119</v>
       </c>
       <c r="R12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -1868,69 +1940,75 @@
         <v>0</v>
       </c>
       <c r="V12">
+        <v>-36.18354089815817</v>
+      </c>
+      <c r="W12">
+        <v>-0.7912490178082052</v>
+      </c>
+      <c r="X12">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W12">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X12">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y12">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.8299339386406256</v>
+        <v>0</v>
       </c>
       <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
         <v>0.9672774162565773</v>
       </c>
-      <c r="AD12">
+      <c r="AF12">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE12">
+      <c r="AG12">
         <v>0.6825109449106408</v>
       </c>
-      <c r="AF12">
-        <v>-31.05493576886262</v>
-      </c>
-      <c r="AG12">
-        <v>-31.19658119658119</v>
-      </c>
       <c r="AH12">
-        <v>-5.778208719385184</v>
+        <v>-26.25257461158482</v>
       </c>
       <c r="AI12">
+        <v>-28.72457790408301</v>
+      </c>
+      <c r="AJ12">
+        <v>-8.25021201188337</v>
+      </c>
+      <c r="AK12">
         <v>0.001</v>
       </c>
-      <c r="AJ12">
-        <v>9.182678469311528</v>
-      </c>
-      <c r="AK12">
-        <v>-2.567427654608816</v>
-      </c>
       <c r="AL12">
-        <v>-3.210781064776368</v>
+        <v>5.376703172437014</v>
+      </c>
+      <c r="AM12">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN12">
+        <v>-5.262669073346681</v>
       </c>
     </row>
-    <row r="13" spans="1:38">
+    <row r="13" spans="1:40">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>2018</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E13">
         <v>50</v>
@@ -1972,10 +2050,10 @@
         <v>14.94252873563218</v>
       </c>
       <c r="R13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
@@ -1984,69 +2062,75 @@
         <v>0</v>
       </c>
       <c r="V13">
+        <v>-24.78432683016792</v>
+      </c>
+      <c r="W13">
+        <v>46.09323904817106</v>
+      </c>
+      <c r="X13">
         <v>7.926167209554841</v>
       </c>
-      <c r="W13">
-        <v>3.497124402528464</v>
-      </c>
-      <c r="X13">
-        <v>1.622736097579276</v>
-      </c>
       <c r="Y13">
-        <v>-1.874388304949188</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>5.11986050010774</v>
+        <v>0</v>
       </c>
       <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
         <v>1</v>
       </c>
-      <c r="AB13">
-        <v>-3.497124402528464</v>
-      </c>
-      <c r="AC13">
+      <c r="AD13">
+        <v>-0</v>
+      </c>
+      <c r="AE13">
         <v>0.8826086335403704</v>
       </c>
-      <c r="AD13">
+      <c r="AF13">
         <v>0.84</v>
       </c>
-      <c r="AE13">
+      <c r="AG13">
         <v>0.7413912521739111</v>
       </c>
-      <c r="AF13">
-        <v>16.28594302101494</v>
-      </c>
-      <c r="AG13">
-        <v>15.95008944966925</v>
-      </c>
       <c r="AH13">
-        <v>5.358822768333884</v>
+        <v>15.73957854638889</v>
       </c>
       <c r="AI13">
-        <v>0.9956436158212228</v>
+        <v>15.34105364101053</v>
       </c>
       <c r="AJ13">
-        <v>6.080571292031284</v>
+        <v>5.967858576992604</v>
       </c>
       <c r="AK13">
-        <v>-0.8586988932845637</v>
+        <v>0.9977967295084087</v>
       </c>
       <c r="AL13">
-        <v>6.217521661618448</v>
+        <v>5.387569742141933</v>
+      </c>
+      <c r="AM13">
+        <v>-0.6297435592695845</v>
+      </c>
+      <c r="AN13">
+        <v>6.597602136262189</v>
       </c>
     </row>
-    <row r="14" spans="1:38">
+    <row r="14" spans="1:40">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>2006</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14">
         <v>52</v>
@@ -2088,10 +2172,10 @@
         <v>16.33109619686801</v>
       </c>
       <c r="R14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
@@ -2100,69 +2184,75 @@
         <v>0</v>
       </c>
       <c r="V14">
+        <v>15.65234850965916</v>
+      </c>
+      <c r="W14">
+        <v>0.2893852175487375</v>
+      </c>
+      <c r="X14">
         <v>12.40560949298812</v>
       </c>
-      <c r="W14">
-        <v>3.14083609983384</v>
-      </c>
-      <c r="X14">
-        <v>1.706744969770823</v>
-      </c>
       <c r="Y14">
-        <v>-1.434091130063018</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>4.847581069604663</v>
+        <v>0</v>
       </c>
       <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
         <v>1</v>
       </c>
-      <c r="AB14">
-        <v>-3.14083609983384</v>
-      </c>
-      <c r="AC14">
+      <c r="AD14">
+        <v>-0</v>
+      </c>
+      <c r="AE14">
         <v>0.9368243165076364</v>
       </c>
-      <c r="AD14">
+      <c r="AF14">
         <v>0.4978713599999999</v>
       </c>
-      <c r="AE14">
+      <c r="AG14">
         <v>0.4664179965407274</v>
       </c>
-      <c r="AF14">
-        <v>18.46085294421424</v>
-      </c>
-      <c r="AG14">
-        <v>18.46085294421424</v>
-      </c>
       <c r="AH14">
-        <v>-2.519119217006342</v>
+        <v>18.31905731255421</v>
       </c>
       <c r="AI14">
+        <v>16.92748453157387</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.9857508043659706</v>
+      </c>
+      <c r="AK14">
         <v>0.999</v>
       </c>
-      <c r="AJ14">
-        <v>5.948865361881026</v>
-      </c>
-      <c r="AK14">
-        <v>2.846074341100446</v>
-      </c>
       <c r="AL14">
-        <v>-5.365193558106787</v>
+        <v>5.097629839420638</v>
+      </c>
+      <c r="AM14">
+        <v>4.161274749007029</v>
+      </c>
+      <c r="AN14">
+        <v>-5.147025553373</v>
       </c>
     </row>
-    <row r="15" spans="1:38">
+    <row r="15" spans="1:40">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>2014</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E15">
         <v>50.4</v>
@@ -2204,10 +2294,10 @@
         <v>14.54545454545455</v>
       </c>
       <c r="R15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
@@ -2216,69 +2306,75 @@
         <v>0</v>
       </c>
       <c r="V15">
+        <v>13.28531144661155</v>
+      </c>
+      <c r="W15">
+        <v>0.5566731270803391</v>
+      </c>
+      <c r="X15">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W15">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X15">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y15">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
         <v>1</v>
       </c>
-      <c r="AB15">
-        <v>-4.810009664065643</v>
-      </c>
-      <c r="AC15">
+      <c r="AD15">
+        <v>-0</v>
+      </c>
+      <c r="AE15">
         <v>0.9188427504203317</v>
       </c>
-      <c r="AD15">
+      <c r="AF15">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE15">
+      <c r="AG15">
         <v>0.648335444696586</v>
       </c>
-      <c r="AF15">
-        <v>14.40930571032542</v>
-      </c>
-      <c r="AG15">
-        <v>14.54545454545455</v>
-      </c>
       <c r="AH15">
-        <v>-0.703469971762658</v>
+        <v>14.91926043901995</v>
       </c>
       <c r="AI15">
-        <v>0.9424778302077692</v>
+        <v>14.73235749223725</v>
       </c>
       <c r="AJ15">
-        <v>9.229820350813995</v>
+        <v>-0.8903729185453599</v>
       </c>
       <c r="AK15">
-        <v>-2.567427654608816</v>
+        <v>0.9983850508270111</v>
       </c>
       <c r="AL15">
-        <v>1.863957682846158</v>
+        <v>5.002555534632684</v>
+      </c>
+      <c r="AM15">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN15">
+        <v>2.09717001999133</v>
       </c>
     </row>
-    <row r="16" spans="1:38">
+    <row r="16" spans="1:40">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>2018</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E16">
         <v>52</v>
@@ -2320,10 +2416,10 @@
         <v>8.672936259143157</v>
       </c>
       <c r="R16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T16" t="b">
         <v>0</v>
@@ -2332,69 +2428,75 @@
         <v>0</v>
       </c>
       <c r="V16">
+        <v>6.505602308655734</v>
+      </c>
+      <c r="W16">
+        <v>0.1256974260922776</v>
+      </c>
+      <c r="X16">
         <v>7.926167209554841</v>
       </c>
-      <c r="W16">
-        <v>3.497124402528464</v>
-      </c>
-      <c r="X16">
-        <v>1.622736097579276</v>
-      </c>
       <c r="Y16">
-        <v>-1.874388304949188</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>5.11986050010774</v>
+        <v>0</v>
       </c>
       <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
         <v>1</v>
       </c>
-      <c r="AB16">
-        <v>-3.497124402528464</v>
-      </c>
-      <c r="AC16">
+      <c r="AD16">
+        <v>-0</v>
+      </c>
+      <c r="AE16">
         <v>0.9685305364313507</v>
       </c>
-      <c r="AD16">
+      <c r="AF16">
         <v>0.84</v>
       </c>
-      <c r="AE16">
+      <c r="AG16">
         <v>0.8135656506023345</v>
       </c>
-      <c r="AF16">
-        <v>13.84596845774055</v>
-      </c>
-      <c r="AG16">
-        <v>12.5527104080912</v>
-      </c>
       <c r="AH16">
-        <v>-5.921410673343185</v>
+        <v>13.90071227596027</v>
       </c>
       <c r="AI16">
-        <v>0.9802133371119082</v>
+        <v>11.28682426755171</v>
       </c>
       <c r="AJ16">
-        <v>6.098951576280304</v>
+        <v>-4.6555245328037</v>
       </c>
       <c r="AK16">
-        <v>-0.8586988932845637</v>
+        <v>0.980343280570425</v>
       </c>
       <c r="AL16">
-        <v>-5.062711780058621</v>
+        <v>5.4766720780999</v>
+      </c>
+      <c r="AM16">
+        <v>-0.6297435592695845</v>
+      </c>
+      <c r="AN16">
+        <v>-4.025780973534115</v>
       </c>
     </row>
-    <row r="17" spans="1:38">
+    <row r="17" spans="1:40">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17">
         <v>2006</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E17">
         <v>48.5</v>
@@ -2436,10 +2538,10 @@
         <v>3.191489361702125</v>
       </c>
       <c r="R17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T17" t="b">
         <v>0</v>
@@ -2448,69 +2550,75 @@
         <v>1</v>
       </c>
       <c r="V17">
+        <v>0.8762499846250382</v>
+      </c>
+      <c r="W17">
+        <v>0.01651553615485102</v>
+      </c>
+      <c r="X17">
         <v>12.40560949298812</v>
       </c>
-      <c r="W17">
-        <v>3.14083609983384</v>
-      </c>
-      <c r="X17">
-        <v>1.706744969770823</v>
-      </c>
       <c r="Y17">
-        <v>-1.434091130063018</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>4.847581069604663</v>
+        <v>0</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.706744969770823</v>
+        <v>0</v>
       </c>
       <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
         <v>0.9570945616813419</v>
       </c>
-      <c r="AD17">
+      <c r="AF17">
         <v>0.4978713599999999</v>
       </c>
-      <c r="AE17">
+      <c r="AG17">
         <v>0.4765099710728935</v>
       </c>
-      <c r="AF17">
-        <v>0.1996077540085479</v>
-      </c>
-      <c r="AG17">
-        <v>0.1996077540085479</v>
-      </c>
       <c r="AH17">
-        <v>0.6931577667713413</v>
+        <v>2.412858983135079</v>
       </c>
       <c r="AI17">
-        <v>0.5135974941786274</v>
+        <v>2.957900248132011</v>
       </c>
       <c r="AJ17">
-        <v>5.855237004157829</v>
+        <v>-2.065134727352122</v>
       </c>
       <c r="AK17">
-        <v>2.846074341100446</v>
+        <v>0.7226330607390499</v>
       </c>
       <c r="AL17">
-        <v>-2.152916574329105</v>
+        <v>5.007606455730596</v>
+      </c>
+      <c r="AM17">
+        <v>4.161274749007029</v>
+      </c>
+      <c r="AN17">
+        <v>-6.226409476359152</v>
       </c>
     </row>
-    <row r="18" spans="1:38">
+    <row r="18" spans="1:40">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>2014</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E18">
         <v>34.7</v>
@@ -2552,10 +2660,10 @@
         <v>20.59496567505721</v>
       </c>
       <c r="R18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
@@ -2564,69 +2672,75 @@
         <v>1</v>
       </c>
       <c r="V18">
+        <v>-17.71779161010853</v>
+      </c>
+      <c r="W18">
+        <v>-0.3897089008254575</v>
+      </c>
+      <c r="X18">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W18">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X18">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y18">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
         <v>1</v>
       </c>
-      <c r="AB18">
-        <v>-4.810009664065643</v>
-      </c>
-      <c r="AC18">
+      <c r="AD18">
+        <v>-0</v>
+      </c>
+      <c r="AE18">
         <v>0.9248223613213513</v>
       </c>
-      <c r="AD18">
+      <c r="AF18">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE18">
+      <c r="AG18">
         <v>0.6525546581483453</v>
       </c>
-      <c r="AF18">
-        <v>-20.58799263487226</v>
-      </c>
-      <c r="AG18">
-        <v>-20.59496567505721</v>
-      </c>
       <c r="AH18">
-        <v>2.487465164123222</v>
+        <v>-17.35244818736504</v>
       </c>
       <c r="AI18">
-        <v>0.01667791405759628</v>
+        <v>-18.97370693121113</v>
       </c>
       <c r="AJ18">
-        <v>9.679113437771917</v>
+        <v>0.8662064202771376</v>
       </c>
       <c r="AK18">
-        <v>-2.567427654608816</v>
+        <v>0.001</v>
       </c>
       <c r="AL18">
-        <v>5.054892818732037</v>
+        <v>5.211290935515061</v>
+      </c>
+      <c r="AM18">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN18">
+        <v>3.853749358813828</v>
       </c>
     </row>
-    <row r="19" spans="1:38">
+    <row r="19" spans="1:40">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B19">
         <v>2018</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E19">
         <v>49</v>
@@ -2668,10 +2782,10 @@
         <v>2.317811651701817</v>
       </c>
       <c r="R19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
@@ -2680,69 +2794,75 @@
         <v>0</v>
       </c>
       <c r="V19">
+        <v>3.551460791777688</v>
+      </c>
+      <c r="W19">
+        <v>0.1041874421837981</v>
+      </c>
+      <c r="X19">
         <v>7.926167209554841</v>
       </c>
-      <c r="W19">
-        <v>3.497124402528464</v>
-      </c>
-      <c r="X19">
-        <v>1.622736097579276</v>
-      </c>
       <c r="Y19">
-        <v>-1.874388304949188</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>5.11986050010774</v>
+        <v>0</v>
       </c>
       <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
         <v>1</v>
       </c>
-      <c r="AB19">
-        <v>-3.497124402528464</v>
-      </c>
-      <c r="AC19">
+      <c r="AD19">
+        <v>-0</v>
+      </c>
+      <c r="AE19">
         <v>0.9644270734482727</v>
       </c>
-      <c r="AD19">
+      <c r="AF19">
         <v>0.84</v>
       </c>
-      <c r="AE19">
+      <c r="AG19">
         <v>0.8101187416965491</v>
       </c>
-      <c r="AF19">
-        <v>6.469545348436421</v>
-      </c>
-      <c r="AG19">
-        <v>5.431611924252771</v>
-      </c>
       <c r="AH19">
-        <v>-1.775963690291285</v>
+        <v>7.18984701924839</v>
       </c>
       <c r="AI19">
-        <v>0.824784844198285</v>
+        <v>4.753829335475103</v>
       </c>
       <c r="AJ19">
-        <v>5.816956485122046</v>
+        <v>-1.098181101513617</v>
       </c>
       <c r="AK19">
-        <v>-0.8586988932845637</v>
+        <v>0.8050802767962357</v>
       </c>
       <c r="AL19">
-        <v>-0.9172647970067208</v>
+        <v>5.528296292290408</v>
+      </c>
+      <c r="AM19">
+        <v>-0.6297435592695845</v>
+      </c>
+      <c r="AN19">
+        <v>-0.4684375422440329</v>
       </c>
     </row>
-    <row r="20" spans="1:38">
+    <row r="20" spans="1:40">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20">
         <v>2006</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E20">
         <v>54</v>
@@ -2784,10 +2904,10 @@
         <v>22.72727272727273</v>
       </c>
       <c r="R20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T20" t="b">
         <v>0</v>
@@ -2796,69 +2916,75 @@
         <v>0</v>
       </c>
       <c r="V20">
+        <v>27.7655845866058</v>
+      </c>
+      <c r="W20">
+        <v>-0.005584586605802855</v>
+      </c>
+      <c r="X20">
         <v>12.40560949298812</v>
       </c>
-      <c r="W20">
-        <v>3.14083609983384</v>
-      </c>
-      <c r="X20">
-        <v>1.706744969770823</v>
-      </c>
       <c r="Y20">
-        <v>-1.434091130063018</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>4.847581069604663</v>
+        <v>0</v>
       </c>
       <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
         <v>1</v>
       </c>
-      <c r="AB20">
-        <v>-3.14083609983384</v>
-      </c>
-      <c r="AC20">
+      <c r="AD20">
+        <v>-0</v>
+      </c>
+      <c r="AE20">
         <v>0.9380831519646859</v>
       </c>
-      <c r="AD20">
+      <c r="AF20">
         <v>0.4978713599999999</v>
       </c>
-      <c r="AE20">
+      <c r="AG20">
         <v>0.4670447346617448</v>
       </c>
-      <c r="AF20">
-        <v>25.87394263072278</v>
-      </c>
-      <c r="AG20">
-        <v>25.87394263072278</v>
-      </c>
       <c r="AH20">
-        <v>1.886057369277218</v>
+        <v>24.85999140804866</v>
       </c>
       <c r="AI20">
+        <v>23.36708833150551</v>
+      </c>
+      <c r="AJ20">
+        <v>4.392911668494492</v>
+      </c>
+      <c r="AK20">
         <v>0.999</v>
       </c>
-      <c r="AJ20">
-        <v>5.603832645487631</v>
-      </c>
-      <c r="AK20">
-        <v>2.846074341100446</v>
-      </c>
       <c r="AL20">
-        <v>-0.9600169718232281</v>
+        <v>4.927182409501452</v>
+      </c>
+      <c r="AM20">
+        <v>4.161274749007029</v>
+      </c>
+      <c r="AN20">
+        <v>0.2316369194874621</v>
       </c>
     </row>
-    <row r="21" spans="1:38">
+    <row r="21" spans="1:40">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B21">
         <v>2014</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E21">
         <v>32</v>
@@ -2900,10 +3026,10 @@
         <v>26.43678160919541</v>
       </c>
       <c r="R21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T21" t="b">
         <v>0</v>
@@ -2912,69 +3038,75 @@
         <v>0</v>
       </c>
       <c r="V21">
+        <v>-32.85153524559672</v>
+      </c>
+      <c r="W21">
+        <v>-1.427917952775388</v>
+      </c>
+      <c r="X21">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W21">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X21">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y21">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.8299339386406256</v>
+        <v>0</v>
       </c>
       <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
         <v>0.9130832382647269</v>
       </c>
-      <c r="AD21">
+      <c r="AF21">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE21">
+      <c r="AG21">
         <v>0.6442715329195913</v>
       </c>
-      <c r="AF21">
-        <v>-26.69593762345981</v>
-      </c>
-      <c r="AG21">
-        <v>-26.43678160919541</v>
-      </c>
       <c r="AH21">
-        <v>-7.842671589176696</v>
+        <v>-26.65827706309963</v>
       </c>
       <c r="AI21">
-        <v>0.002313520794631751</v>
+        <v>-26.54752933614752</v>
       </c>
       <c r="AJ21">
-        <v>9.335308074074499</v>
+        <v>-7.73192386222459</v>
       </c>
       <c r="AK21">
-        <v>-2.567427654608816</v>
+        <v>0.001</v>
       </c>
       <c r="AL21">
-        <v>-5.275243934567881</v>
+        <v>5.143590432278981</v>
+      </c>
+      <c r="AM21">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN21">
+        <v>-4.744380923687901</v>
       </c>
     </row>
-    <row r="22" spans="1:38">
+    <row r="22" spans="1:40">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B22">
         <v>2018</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E22">
         <v>39</v>
@@ -3016,10 +3148,10 @@
         <v>16.12903225806451</v>
       </c>
       <c r="R22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T22" t="b">
         <v>0</v>
@@ -3028,69 +3160,75 @@
         <v>0</v>
       </c>
       <c r="V22">
+        <v>-19.06384902766271</v>
+      </c>
+      <c r="W22">
+        <v>-0.7367947268799178</v>
+      </c>
+      <c r="X22">
         <v>7.926167209554841</v>
       </c>
-      <c r="W22">
-        <v>3.497124402528464</v>
-      </c>
-      <c r="X22">
-        <v>1.622736097579276</v>
-      </c>
       <c r="Y22">
-        <v>-1.874388304949188</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>5.11986050010774</v>
+        <v>0</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.622736097579276</v>
+        <v>0</v>
       </c>
       <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
         <v>0.9464053042962091</v>
       </c>
-      <c r="AD22">
+      <c r="AF22">
         <v>0.84</v>
       </c>
-      <c r="AE22">
+      <c r="AG22">
         <v>0.7949804556088156</v>
       </c>
-      <c r="AF22">
-        <v>-15.23314016592376</v>
-      </c>
-      <c r="AG22">
-        <v>-15.45711318895895</v>
-      </c>
       <c r="AH22">
-        <v>-4.343530565583677</v>
+        <v>-14.29398428538185</v>
       </c>
       <c r="AI22">
-        <v>0.002292985927010862</v>
+        <v>-15.21150827172318</v>
       </c>
       <c r="AJ22">
-        <v>5.45270068693277</v>
+        <v>-4.589135482819447</v>
       </c>
       <c r="AK22">
-        <v>-0.8586988932845637</v>
+        <v>0.001</v>
       </c>
       <c r="AL22">
-        <v>-3.484831672299114</v>
+        <v>4.887026893204637</v>
+      </c>
+      <c r="AM22">
+        <v>-0.6297435592695845</v>
+      </c>
+      <c r="AN22">
+        <v>-3.959391923549863</v>
       </c>
     </row>
-    <row r="23" spans="1:38">
+    <row r="23" spans="1:40">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B23">
         <v>2010</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E23">
         <v>39.3</v>
@@ -3132,10 +3270,10 @@
         <v>16.91331923890063</v>
       </c>
       <c r="R23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T23" t="b">
         <v>0</v>
@@ -3144,69 +3282,75 @@
         <v>0</v>
       </c>
       <c r="V23">
+        <v>-23.23964724769633</v>
+      </c>
+      <c r="W23">
+        <v>-0.7339446648268826</v>
+      </c>
+      <c r="X23">
         <v>-10.21739130434782</v>
       </c>
-      <c r="W23">
-        <v>6.472354736093108</v>
-      </c>
-      <c r="X23">
-        <v>0.2591279874364147</v>
-      </c>
       <c r="Y23">
-        <v>-6.213226748656693</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>6.731482723529522</v>
+        <v>0</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.2591279874364147</v>
+        <v>0</v>
       </c>
       <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
         <v>0.9576285292324994</v>
       </c>
-      <c r="AD23">
+      <c r="AF23">
         <v>0.5927039999999999</v>
       </c>
-      <c r="AE23">
+      <c r="AG23">
         <v>0.5675902597902193</v>
       </c>
-      <c r="AF23">
-        <v>-19.56947061159492</v>
-      </c>
-      <c r="AG23">
+      <c r="AH23">
+        <v>-16.94198785852129</v>
+      </c>
+      <c r="AI23">
         <v>-16.91331923890063</v>
       </c>
-      <c r="AH23">
+      <c r="AJ23">
         <v>-7.060272673622585</v>
       </c>
-      <c r="AI23">
+      <c r="AK23">
         <v>0.002189031097677974</v>
       </c>
-      <c r="AJ23">
+      <c r="AL23">
         <v>5.935427559338342</v>
       </c>
-      <c r="AK23">
+      <c r="AM23">
         <v>-6.252657710366077</v>
       </c>
-      <c r="AL23">
+      <c r="AN23">
         <v>-0.8076149632565075</v>
       </c>
     </row>
-    <row r="24" spans="1:38">
+    <row r="24" spans="1:40">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B24">
         <v>2014</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E24">
         <v>48.8</v>
@@ -3248,10 +3392,10 @@
         <v>0.8264462809917319</v>
       </c>
       <c r="R24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T24" t="b">
         <v>0</v>
@@ -3260,69 +3404,75 @@
         <v>0</v>
       </c>
       <c r="V24">
+        <v>3.24422985133942</v>
+      </c>
+      <c r="W24">
+        <v>0.01653065834253109</v>
+      </c>
+      <c r="X24">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W24">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X24">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y24">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
         <v>1</v>
       </c>
-      <c r="AB24">
-        <v>-4.810009664065643</v>
-      </c>
-      <c r="AC24">
+      <c r="AD24">
+        <v>-0</v>
+      </c>
+      <c r="AE24">
         <v>0.9822451832409258</v>
       </c>
-      <c r="AD24">
+      <c r="AF24">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE24">
+      <c r="AG24">
         <v>0.6930722012947972</v>
       </c>
-      <c r="AF24">
-        <v>1.078946189422229</v>
-      </c>
-      <c r="AG24">
-        <v>0.8264462809917319</v>
-      </c>
       <c r="AH24">
-        <v>2.434314228690219</v>
+        <v>4.27076693820225</v>
       </c>
       <c r="AI24">
-        <v>0.533886607841855</v>
+        <v>2.548606609596991</v>
       </c>
       <c r="AJ24">
-        <v>9.717920735471186</v>
+        <v>0.7121539000849602</v>
       </c>
       <c r="AK24">
-        <v>-2.567427654608816</v>
+        <v>0.6704581009655978</v>
       </c>
       <c r="AL24">
-        <v>5.001741883299035</v>
+        <v>5.776815458648815</v>
+      </c>
+      <c r="AM24">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN24">
+        <v>3.69969683862165</v>
       </c>
     </row>
-    <row r="25" spans="1:38">
+    <row r="25" spans="1:40">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B25">
         <v>2022</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E25">
         <v>48.7</v>
@@ -3364,10 +3514,10 @@
         <v>1.458333333333329</v>
       </c>
       <c r="R25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T25" t="b">
         <v>0</v>
@@ -3376,69 +3526,75 @@
         <v>0</v>
       </c>
       <c r="V25">
+        <v>9.156407262772259</v>
+      </c>
+      <c r="W25">
+        <v>0.1870012943603818</v>
+      </c>
+      <c r="X25">
         <v>-2.67379679144385</v>
       </c>
-      <c r="W25">
-        <v>3.770648896483239</v>
-      </c>
-      <c r="X25">
-        <v>2.083268974682547</v>
-      </c>
       <c r="Y25">
-        <v>-1.687379921800692</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>5.853917871165787</v>
+        <v>0</v>
       </c>
       <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
         <v>1</v>
       </c>
-      <c r="AB25">
-        <v>-3.770648896483239</v>
-      </c>
-      <c r="AC25">
-        <v>0.9696019801959977</v>
-      </c>
       <c r="AD25">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="AE25">
         <v>0.9696019801959977</v>
       </c>
       <c r="AF25">
-        <v>2.782615202862778</v>
+        <v>1</v>
       </c>
       <c r="AG25">
-        <v>2.451544735480415</v>
+        <v>0.9696019801959977</v>
       </c>
       <c r="AH25">
-        <v>6.891863821652225</v>
+        <v>0.8114823295549364</v>
       </c>
       <c r="AI25">
-        <v>0.6776531336285638</v>
+        <v>0.8114823295549364</v>
       </c>
       <c r="AJ25">
-        <v>5.316198743380979</v>
+        <v>8.531926227577705</v>
       </c>
       <c r="AK25">
-        <v>2.12594030235794</v>
+        <v>0.5503335079946322</v>
       </c>
       <c r="AL25">
-        <v>4.765923519294285</v>
+        <v>6.414677308281327</v>
+      </c>
+      <c r="AM25">
+        <v>4.262691039343795</v>
+      </c>
+      <c r="AN25">
+        <v>4.269235188233909</v>
       </c>
     </row>
-    <row r="26" spans="1:38">
+    <row r="26" spans="1:40">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B26">
         <v>2010</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E26">
         <v>37.5</v>
@@ -3480,10 +3636,10 @@
         <v>14.57858769931663</v>
       </c>
       <c r="R26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -3492,69 +3648,75 @@
         <v>0</v>
       </c>
       <c r="V26">
+        <v>-11.76551523469792</v>
+      </c>
+      <c r="W26">
+        <v>-0.2516521472763262</v>
+      </c>
+      <c r="X26">
         <v>-10.21739130434782</v>
       </c>
-      <c r="W26">
-        <v>6.472354736093108</v>
-      </c>
-      <c r="X26">
-        <v>0.2591279874364147</v>
-      </c>
       <c r="Y26">
-        <v>-6.213226748656693</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>6.731482723529522</v>
+        <v>0</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.2591279874364147</v>
+        <v>0</v>
       </c>
       <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
         <v>0.9269362437622126</v>
       </c>
-      <c r="AD26">
+      <c r="AF26">
         <v>0.5927039999999999</v>
       </c>
-      <c r="AE26">
+      <c r="AG26">
         <v>0.5493988194228384</v>
       </c>
-      <c r="AF26">
-        <v>-17.56764752317505</v>
-      </c>
-      <c r="AG26">
+      <c r="AH26">
+        <v>-14.94716851103501</v>
+      </c>
+      <c r="AI26">
         <v>-14.57858769931663</v>
       </c>
-      <c r="AH26">
+      <c r="AJ26">
         <v>2.561420317342382</v>
       </c>
-      <c r="AI26">
+      <c r="AK26">
         <v>0.007404180787180031</v>
       </c>
-      <c r="AJ26">
+      <c r="AL26">
         <v>5.982107184872843</v>
       </c>
-      <c r="AK26">
+      <c r="AM26">
         <v>-6.252657710366077</v>
       </c>
-      <c r="AL26">
+      <c r="AN26">
         <v>8.814078027708458</v>
       </c>
     </row>
-    <row r="27" spans="1:38">
+    <row r="27" spans="1:40">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B27">
         <v>2014</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E27">
         <v>45.2</v>
@@ -3596,10 +3758,10 @@
         <v>1.345291479820631</v>
       </c>
       <c r="R27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T27" t="b">
         <v>1</v>
@@ -3608,69 +3770,75 @@
         <v>1</v>
       </c>
       <c r="V27">
+        <v>-1.564446103137224</v>
+      </c>
+      <c r="W27">
+        <v>-0.05920085772870931</v>
+      </c>
+      <c r="X27">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W27">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X27">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y27">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
         <v>1</v>
       </c>
-      <c r="AB27">
-        <v>-4.810009664065643</v>
-      </c>
-      <c r="AC27">
+      <c r="AD27">
+        <v>-0</v>
+      </c>
+      <c r="AE27">
         <v>0.9257610922910944</v>
       </c>
-      <c r="AD27">
+      <c r="AF27">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE27">
+      <c r="AG27">
         <v>0.6532170267205961</v>
       </c>
-      <c r="AF27">
-        <v>1.204858019955478</v>
-      </c>
-      <c r="AG27">
-        <v>1.345291479820631</v>
-      </c>
       <c r="AH27">
-        <v>-2.968938440686564</v>
+        <v>0.3802548163930437</v>
       </c>
       <c r="AI27">
-        <v>0.5564220201073067</v>
+        <v>0.8627731481068373</v>
       </c>
       <c r="AJ27">
-        <v>9.480303448039768</v>
+        <v>-2.486420108972771</v>
       </c>
       <c r="AK27">
-        <v>-2.567427654608816</v>
+        <v>0.5650394724382881</v>
       </c>
       <c r="AL27">
-        <v>-0.4015107860777483</v>
+        <v>5.268561684149072</v>
+      </c>
+      <c r="AM27">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN27">
+        <v>0.5011228295639194</v>
       </c>
     </row>
-    <row r="28" spans="1:38">
+    <row r="28" spans="1:40">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B28">
         <v>2022</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E28">
         <v>44.8</v>
@@ -3712,10 +3880,10 @@
         <v>6.471816283924845</v>
       </c>
       <c r="R28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T28" t="b">
         <v>0</v>
@@ -3724,69 +3892,75 @@
         <v>0</v>
       </c>
       <c r="V28">
+        <v>-3.225740634946544</v>
+      </c>
+      <c r="W28">
+        <v>-0.07793124804414786</v>
+      </c>
+      <c r="X28">
         <v>-2.67379679144385</v>
       </c>
-      <c r="W28">
-        <v>3.770648896483239</v>
-      </c>
-      <c r="X28">
-        <v>2.083268974682547</v>
-      </c>
       <c r="Y28">
-        <v>-1.687379921800692</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>5.853917871165787</v>
+        <v>0</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>2.083268974682547</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>0.9677998760074317</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE28">
         <v>0.9677998760074317</v>
       </c>
       <c r="AF28">
-        <v>-8.444529015258723</v>
+        <v>1</v>
       </c>
       <c r="AG28">
-        <v>-7.951350832425254</v>
+        <v>0.9677998760074317</v>
       </c>
       <c r="AH28">
-        <v>4.647678949434562</v>
+        <v>-9.800259899000016</v>
       </c>
       <c r="AI28">
-        <v>0.06692398885461097</v>
+        <v>-9.800259899000016</v>
       </c>
       <c r="AJ28">
-        <v>5.304086907287133</v>
+        <v>6.496588016009325</v>
       </c>
       <c r="AK28">
-        <v>2.12594030235794</v>
+        <v>0.05562120441023274</v>
       </c>
       <c r="AL28">
-        <v>2.521738647076622</v>
+        <v>6.153493076600435</v>
+      </c>
+      <c r="AM28">
+        <v>4.262691039343795</v>
+      </c>
+      <c r="AN28">
+        <v>2.233896976665529</v>
       </c>
     </row>
-    <row r="29" spans="1:38">
+    <row r="29" spans="1:40">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B29">
         <v>2006</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E29">
         <v>53.3</v>
@@ -3828,10 +4002,10 @@
         <v>10.351966873706</v>
       </c>
       <c r="R29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T29" t="b">
         <v>0</v>
@@ -3840,69 +4014,75 @@
         <v>1</v>
       </c>
       <c r="V29">
+        <v>12.34891407222666</v>
+      </c>
+      <c r="W29">
+        <v>-0.006445578527921825</v>
+      </c>
+      <c r="X29">
         <v>12.40560949298812</v>
       </c>
-      <c r="W29">
-        <v>3.14083609983384</v>
-      </c>
-      <c r="X29">
-        <v>1.706744969770823</v>
-      </c>
       <c r="Y29">
-        <v>-1.434091130063018</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>4.847581069604663</v>
+        <v>0</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.706744969770823</v>
+        <v>0</v>
       </c>
       <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
         <v>0.9827546998106902</v>
       </c>
-      <c r="AD29">
+      <c r="AF29">
         <v>0.4978713599999999</v>
       </c>
-      <c r="AE29">
+      <c r="AG29">
         <v>0.48928541894114</v>
       </c>
-      <c r="AF29">
-        <v>10.67099907079506</v>
-      </c>
-      <c r="AG29">
-        <v>10.67099907079506</v>
-      </c>
       <c r="AH29">
-        <v>1.671469422903677</v>
+        <v>11.68950373246543</v>
       </c>
       <c r="AI29">
-        <v>0.9651456379123636</v>
+        <v>10.75322793133383</v>
       </c>
       <c r="AJ29">
-        <v>5.883232315516177</v>
+        <v>1.589240562364909</v>
       </c>
       <c r="AK29">
-        <v>2.846074341100446</v>
+        <v>0.9764487606055239</v>
       </c>
       <c r="AL29">
-        <v>-1.174604918196769</v>
+        <v>5.416213044670446</v>
+      </c>
+      <c r="AM29">
+        <v>4.161274749007029</v>
+      </c>
+      <c r="AN29">
+        <v>-2.572034186642121</v>
       </c>
     </row>
-    <row r="30" spans="1:38">
+    <row r="30" spans="1:40">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B30">
         <v>2010</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E30">
         <v>37</v>
@@ -3944,81 +4124,87 @@
         <v>21.69312169312168</v>
       </c>
       <c r="R30" t="s">
+        <v>51</v>
+      </c>
+      <c r="S30" t="s">
+        <v>51</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>-17.4424090809725</v>
+      </c>
+      <c r="W30">
+        <v>-0.687461048897628</v>
+      </c>
+      <c r="X30">
+        <v>-10.21739130434782</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0.9537098615407098</v>
+      </c>
+      <c r="AF30">
+        <v>0.5927039999999999</v>
+      </c>
+      <c r="AG30">
+        <v>0.5652676497746247</v>
+      </c>
+      <c r="AH30">
+        <v>-21.73515267677366</v>
+      </c>
+      <c r="AI30">
+        <v>-21.69312169312168</v>
+      </c>
+      <c r="AJ30">
+        <v>3.563251563251555</v>
+      </c>
+      <c r="AK30">
+        <v>0.001</v>
+      </c>
+      <c r="AL30">
+        <v>5.869273590017441</v>
+      </c>
+      <c r="AM30">
+        <v>-6.252657710366077</v>
+      </c>
+      <c r="AN30">
+        <v>9.815909273617631</v>
+      </c>
+    </row>
+    <row r="31" spans="1:40">
+      <c r="A31" t="s">
         <v>49</v>
-      </c>
-      <c r="S30" t="s">
-        <v>49</v>
-      </c>
-      <c r="T30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>-10.21739130434782</v>
-      </c>
-      <c r="W30">
-        <v>6.472354736093108</v>
-      </c>
-      <c r="X30">
-        <v>0.2591279874364147</v>
-      </c>
-      <c r="Y30">
-        <v>-6.213226748656693</v>
-      </c>
-      <c r="Z30">
-        <v>6.731482723529522</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0.2591279874364147</v>
-      </c>
-      <c r="AC30">
-        <v>0.9537098615407098</v>
-      </c>
-      <c r="AD30">
-        <v>0.5927039999999999</v>
-      </c>
-      <c r="AE30">
-        <v>0.5652676497746247</v>
-      </c>
-      <c r="AF30">
-        <v>-24.36362353680956</v>
-      </c>
-      <c r="AG30">
-        <v>-21.69312169312168</v>
-      </c>
-      <c r="AH30">
-        <v>3.563251563251555</v>
-      </c>
-      <c r="AI30">
-        <v>0.001</v>
-      </c>
-      <c r="AJ30">
-        <v>5.869273590017441</v>
-      </c>
-      <c r="AK30">
-        <v>-6.252657710366077</v>
-      </c>
-      <c r="AL30">
-        <v>9.815909273617631</v>
-      </c>
-    </row>
-    <row r="31" spans="1:38">
-      <c r="A31" t="s">
-        <v>47</v>
       </c>
       <c r="B31">
         <v>2018</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E31">
         <v>46</v>
@@ -4060,10 +4246,10 @@
         <v>10.8433734939759</v>
       </c>
       <c r="R31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
@@ -4072,69 +4258,75 @@
         <v>0</v>
       </c>
       <c r="V31">
+        <v>6.845771541305195</v>
+      </c>
+      <c r="W31">
+        <v>-0.02440726845061469</v>
+      </c>
+      <c r="X31">
         <v>7.926167209554841</v>
       </c>
-      <c r="W31">
-        <v>3.497124402528464</v>
-      </c>
-      <c r="X31">
-        <v>1.622736097579276</v>
-      </c>
       <c r="Y31">
-        <v>-1.874388304949188</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>5.11986050010774</v>
+        <v>0</v>
       </c>
       <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
         <v>1</v>
       </c>
-      <c r="AB31">
-        <v>-3.497124402528464</v>
-      </c>
-      <c r="AC31">
+      <c r="AD31">
+        <v>-0</v>
+      </c>
+      <c r="AE31">
         <v>0.910952249022966</v>
       </c>
-      <c r="AD31">
+      <c r="AF31">
         <v>0.84</v>
       </c>
-      <c r="AE31">
+      <c r="AG31">
         <v>0.7651998891792914</v>
       </c>
-      <c r="AF31">
-        <v>9.254734841897383</v>
-      </c>
-      <c r="AG31">
-        <v>9.651894504917014</v>
-      </c>
       <c r="AH31">
-        <v>-2.830530232062433</v>
+        <v>9.1637449066593</v>
       </c>
       <c r="AI31">
-        <v>0.9644598621575147</v>
+        <v>10.0035592003176</v>
       </c>
       <c r="AJ31">
-        <v>5.347415870950532</v>
+        <v>-3.182194927463021</v>
       </c>
       <c r="AK31">
-        <v>-0.8586988932845637</v>
+        <v>0.9791016028618784</v>
       </c>
       <c r="AL31">
-        <v>-1.971831338777869</v>
+        <v>4.91445526193885</v>
+      </c>
+      <c r="AM31">
+        <v>-0.6297435592695845</v>
+      </c>
+      <c r="AN31">
+        <v>-2.552451368193437</v>
       </c>
     </row>
-    <row r="32" spans="1:38">
+    <row r="32" spans="1:40">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B32">
         <v>2022</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E32">
         <v>43.8</v>
@@ -4176,10 +4368,10 @@
         <v>8.368200836820087</v>
       </c>
       <c r="R32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T32" t="b">
         <v>0</v>
@@ -4188,69 +4380,75 @@
         <v>0</v>
       </c>
       <c r="V32">
+        <v>-6.111882346053149</v>
+      </c>
+      <c r="W32">
+        <v>-0.001174182210982089</v>
+      </c>
+      <c r="X32">
         <v>-2.67379679144385</v>
       </c>
-      <c r="W32">
-        <v>3.770648896483239</v>
-      </c>
-      <c r="X32">
-        <v>2.083268974682547</v>
-      </c>
       <c r="Y32">
-        <v>-1.687379921800692</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>5.853917871165787</v>
+        <v>0</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>2.083268974682547</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>0.9775080562327862</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE32">
         <v>0.9775080562327862</v>
       </c>
       <c r="AF32">
-        <v>-9.955940524015368</v>
+        <v>1</v>
       </c>
       <c r="AG32">
-        <v>-9.559005602216548</v>
+        <v>0.9775080562327862</v>
       </c>
       <c r="AH32">
-        <v>3.445949073952416</v>
+        <v>-11.31966445305881</v>
       </c>
       <c r="AI32">
-        <v>0.03700245138239838</v>
+        <v>-11.31966445305881</v>
       </c>
       <c r="AJ32">
-        <v>5.350440096094329</v>
+        <v>5.206607924794682</v>
       </c>
       <c r="AK32">
-        <v>2.12594030235794</v>
+        <v>0.03127544667373272</v>
       </c>
       <c r="AL32">
-        <v>1.320008771594476</v>
+        <v>6.078095009157831</v>
+      </c>
+      <c r="AM32">
+        <v>4.262691039343795</v>
+      </c>
+      <c r="AN32">
+        <v>0.9439168854508866</v>
       </c>
     </row>
-    <row r="33" spans="1:38">
+    <row r="33" spans="1:40">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B33">
         <v>2006</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E33">
         <v>29</v>
@@ -4292,10 +4490,10 @@
         <v>38.29787234042553</v>
       </c>
       <c r="R33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T33" t="b">
         <v>0</v>
@@ -4304,69 +4502,75 @@
         <v>0</v>
       </c>
       <c r="V33">
+        <v>-25.64712470012143</v>
+      </c>
+      <c r="W33">
+        <v>-0.5986544874361286</v>
+      </c>
+      <c r="X33">
         <v>12.40560949298812</v>
       </c>
-      <c r="W33">
-        <v>3.14083609983384</v>
-      </c>
-      <c r="X33">
-        <v>1.706744969770823</v>
-      </c>
       <c r="Y33">
-        <v>-1.434091130063018</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>4.847581069604663</v>
+        <v>0</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.706744969770823</v>
+        <v>0</v>
       </c>
       <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
         <v>0.9584685701680571</v>
       </c>
-      <c r="AD33">
+      <c r="AF33">
         <v>0.4978713599999999</v>
       </c>
-      <c r="AE33">
+      <c r="AG33">
         <v>0.477194050546826</v>
       </c>
-      <c r="AF33">
-        <v>-35.22880802189839</v>
-      </c>
-      <c r="AG33">
-        <v>-35.22880802189839</v>
-      </c>
       <c r="AH33">
-        <v>8.983028834340836</v>
+        <v>-35.5447233573444</v>
       </c>
       <c r="AI33">
+        <v>-37.47192764550119</v>
+      </c>
+      <c r="AJ33">
+        <v>11.22614845794363</v>
+      </c>
+      <c r="AK33">
         <v>0.001</v>
       </c>
-      <c r="AJ33">
-        <v>5.712942512816499</v>
-      </c>
-      <c r="AK33">
-        <v>2.846074341100446</v>
-      </c>
       <c r="AL33">
-        <v>6.13695449324039</v>
+        <v>5.030974372955976</v>
+      </c>
+      <c r="AM33">
+        <v>4.161274749007029</v>
+      </c>
+      <c r="AN33">
+        <v>7.0648737089366</v>
       </c>
     </row>
-    <row r="34" spans="1:38">
+    <row r="34" spans="1:40">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B34">
         <v>2014</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E34">
         <v>31.3</v>
@@ -4408,10 +4612,10 @@
         <v>25.74139976275207</v>
       </c>
       <c r="R34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T34" t="b">
         <v>0</v>
@@ -4420,69 +4624,75 @@
         <v>0</v>
       </c>
       <c r="V34">
+        <v>-27.19549569977184</v>
+      </c>
+      <c r="W34">
+        <v>-1.161468437008807</v>
+      </c>
+      <c r="X34">
         <v>-2.70270270270271</v>
       </c>
-      <c r="W34">
-        <v>4.810009664065643</v>
-      </c>
-      <c r="X34">
-        <v>0.8299339386406256</v>
-      </c>
       <c r="Y34">
-        <v>-3.980075725425018</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>5.639943602706269</v>
+        <v>0</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.8299339386406256</v>
+        <v>0</v>
       </c>
       <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
         <v>0.8992249996524786</v>
       </c>
-      <c r="AD34">
+      <c r="AF34">
         <v>0.7055999999999999</v>
       </c>
-      <c r="AE34">
+      <c r="AG34">
         <v>0.6344931597547888</v>
       </c>
-      <c r="AF34">
-        <v>-26.14945251063233</v>
-      </c>
-      <c r="AG34">
-        <v>-25.74139976275207</v>
-      </c>
       <c r="AH34">
-        <v>-2.615564374028573</v>
+        <v>-27.74299036428698</v>
       </c>
       <c r="AI34">
-        <v>0.002722546360948808</v>
+        <v>-26.74219506351952</v>
       </c>
       <c r="AJ34">
-        <v>9.261326443646645</v>
+        <v>-1.614769073261122</v>
       </c>
       <c r="AK34">
-        <v>-2.567427654608816</v>
+        <v>0.001</v>
       </c>
       <c r="AL34">
-        <v>-0.04813671941975661</v>
+        <v>5.061468655636036</v>
+      </c>
+      <c r="AM34">
+        <v>-2.98754293853669</v>
+      </c>
+      <c r="AN34">
+        <v>1.372773865275568</v>
       </c>
     </row>
-    <row r="35" spans="1:38">
+    <row r="35" spans="1:40">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B35">
         <v>2018</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E35">
         <v>44.5</v>
@@ -4524,10 +4734,10 @@
         <v>7.09812108559499</v>
       </c>
       <c r="R35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T35" t="b">
         <v>0</v>
@@ -4536,55 +4746,61 @@
         <v>0</v>
       </c>
       <c r="V35">
+        <v>-2.567246261342587</v>
+      </c>
+      <c r="W35">
+        <v>-0.01287871346088076</v>
+      </c>
+      <c r="X35">
         <v>7.926167209554841</v>
       </c>
-      <c r="W35">
-        <v>3.497124402528464</v>
-      </c>
-      <c r="X35">
-        <v>1.622736097579276</v>
-      </c>
       <c r="Y35">
-        <v>-1.874388304949188</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>5.11986050010774</v>
+        <v>0</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.622736097579276</v>
+        <v>0</v>
       </c>
       <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
         <v>0.974950050002563</v>
       </c>
-      <c r="AD35">
+      <c r="AF35">
         <v>0.84</v>
       </c>
-      <c r="AE35">
+      <c r="AG35">
         <v>0.8189580420021528</v>
       </c>
-      <c r="AF35">
-        <v>-6.888018315525379</v>
-      </c>
-      <c r="AG35">
-        <v>-6.940544008042782</v>
-      </c>
       <c r="AH35">
-        <v>4.360419033239314</v>
+        <v>-5.619561087991294</v>
       </c>
       <c r="AI35">
-        <v>0.1003470350482054</v>
+        <v>-6.358841086793142</v>
       </c>
       <c r="AJ35">
-        <v>5.424094029065443</v>
+        <v>3.778716111989674</v>
       </c>
       <c r="AK35">
-        <v>-0.8586988932845637</v>
+        <v>0.09465879553502221</v>
       </c>
       <c r="AL35">
-        <v>5.219117926523878</v>
+        <v>4.844460247741853</v>
+      </c>
+      <c r="AM35">
+        <v>-0.6297435592695845</v>
+      </c>
+      <c r="AN35">
+        <v>4.408459671259259</v>
       </c>
     </row>
   </sheetData>
